--- a/output/Data and Chart Outputs/netherlands_cbs_gas_monthly.xlsx
+++ b/output/Data and Chart Outputs/netherlands_cbs_gas_monthly.xlsx
@@ -789,7 +789,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GWh per month = CBS mln m3 (Groningen-equivalent gas, 35.17 MJ/m3 gross calorific value) x 9.769 kWh/m3. Production = winning uit de bodem (gas from Dutch fields); Biomethane = productie uit andere bronnen (chiefly upgraded biogas); Consumption = totaal verbruik (energy companies incl. power plants, own use at production and transport, flaring, final consumers). Imports/exports are pipeline gas by partner and LNG. StockChange: positive = stock build. CBS figures are revised; the table is re-read whole each run.</t>
+          <t>GWh per month = CBS mln m3 (Groningen-equivalent gas, 35.17 MJ/m3 gross calorific value) x 9.769 kWh/m3. Production = winning uit de bodem (gas from Dutch fields); Biomethane = productie uit andere bronnen (chiefly upgraded biogas); Consumption = totaal verbruik (energy companies incl. power plants, own use at production and transport, flaring, final consumers). Imports/exports are pipeline gas by partner and LNG. StockChange: positive = stock build. The Europe master gives the monthly production and consumption a daily shape from ENTSOG's Dutch entries/exits and keeps the CBS monthly totals exactly. CBS figures are revised; the table is re-read whole each run.</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-04 14:32 UTC; 2021-01 to 2026-08</t>
+          <t>2026-10-04 23:09 UTC; 2021-01 to 2026-08</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/netherlands_cbs_gas_monthly.xlsx
+++ b/output/Data and Chart Outputs/netherlands_cbs_gas_monthly.xlsx
@@ -155,7 +155,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Netherlands natural gas balance (CBS) (to Aug/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Netherlands natural gas balance (CBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -191,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$69</f>
+              <f>'Chart'!$B$2:$B$70</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -227,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$69</f>
+              <f>'Chart'!$C$2:$C$70</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -263,12 +264,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$69</f>
+              <f>'Chart'!$D$2:$D$70</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -299,12 +300,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$69</f>
+              <f>'Chart'!$E$2:$E$70</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -335,12 +336,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$69</f>
+              <f>'Chart'!$F$2:$F$70</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -789,7 +790,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GWh per month = CBS mln m3 (Groningen-equivalent gas, 35.17 MJ/m3 gross calorific value) x 9.769 kWh/m3. Production = winning uit de bodem (gas from Dutch fields); Biomethane = productie uit andere bronnen (chiefly upgraded biogas); Consumption = totaal verbruik (energy companies incl. power plants, own use at production and transport, flaring, final consumers). Imports/exports are pipeline gas by partner and LNG. StockChange: positive = stock build. The Europe master gives the monthly production and consumption a daily shape from ENTSOG's Dutch entries/exits and keeps the CBS monthly totals exactly. CBS figures are revised; the table is re-read whole each run.</t>
+          <t>GWh per month = CBS mln m3 (Groningen-equivalent gas, 35.17 MJ/m3 gross calorific value) x 9.769 kWh/m3. Production = winning uit de bodem (gas from Dutch fields); Biomethane = productie uit andere bronnen (chiefly upgraded biogas); Consumption = totaal verbruik (energy companies incl. power plants, own use at production and transport, flaring, final consumers). Imports/exports are pipeline gas by partner and LNG. StockChange (Voorraadmutatie): positive = stock WITHDRAWAL (a supply item: production + imports + StockChange - exports - bunkering = consumption closes only with this sign; it matches the AGSI+ Dutch net withdrawal). The Europe master gives the monthly production and consumption a daily shape from ENTSOG's Dutch entries/exits and keeps the CBS monthly totals exactly. CBS figures are revised; the table is re-read whole each run.</t>
         </is>
       </c>
     </row>
@@ -804,7 +805,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-04 23:09 UTC; 2021-01 to 2026-08</t>
+          <t>2026-10-28 00:55 UTC; 2021-01 to 2026-09</t>
         </is>
       </c>
     </row>
@@ -819,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2074,7 +2075,7 @@
         <v>28.0188</v>
       </c>
       <c r="F62" t="n">
-        <v>43.7085</v>
+        <v>43.728</v>
       </c>
     </row>
     <row r="63">
@@ -2094,7 +2095,7 @@
         <v>25.8597</v>
       </c>
       <c r="F63" t="n">
-        <v>32.6495</v>
+        <v>32.6593</v>
       </c>
     </row>
     <row r="64">
@@ -2154,7 +2155,7 @@
         <v>22.4013</v>
       </c>
       <c r="F66" t="n">
-        <v>19.5389</v>
+        <v>19.5291</v>
       </c>
     </row>
     <row r="67">
@@ -2174,7 +2175,7 @@
         <v>23.476</v>
       </c>
       <c r="F67" t="n">
-        <v>16.1098</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="68">
@@ -2182,19 +2183,19 @@
         <v>46204</v>
       </c>
       <c r="B68" t="n">
-        <v>7.1512</v>
+        <v>7.3662</v>
       </c>
       <c r="C68" t="n">
-        <v>30.1192</v>
+        <v>29.9336</v>
       </c>
       <c r="D68" t="n">
-        <v>14.6249</v>
+        <v>14.6346</v>
       </c>
       <c r="E68" t="n">
         <v>20.2618</v>
       </c>
       <c r="F68" t="n">
-        <v>15.1426</v>
+        <v>15.1622</v>
       </c>
     </row>
     <row r="69">
@@ -2202,19 +2203,39 @@
         <v>46235</v>
       </c>
       <c r="B69" t="n">
-        <v>6.486899999999999</v>
+        <v>7.0535</v>
       </c>
       <c r="C69" t="n">
-        <v>26.0063</v>
+        <v>25.4787</v>
       </c>
       <c r="D69" t="n">
-        <v>22.587</v>
+        <v>22.1669</v>
       </c>
       <c r="E69" t="n">
-        <v>21.864</v>
+        <v>21.8542</v>
       </c>
       <c r="F69" t="n">
         <v>16.3052</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>6.223100000000001</v>
+      </c>
+      <c r="C70" t="n">
+        <v>23.3783</v>
+      </c>
+      <c r="D70" t="n">
+        <v>23.0559</v>
+      </c>
+      <c r="E70" t="n">
+        <v>17.5166</v>
+      </c>
+      <c r="F70" t="n">
+        <v>16.2564</v>
       </c>
     </row>
   </sheetData>
@@ -2229,7 +2250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R69"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5692,7 +5713,7 @@
         <v>7717.9</v>
       </c>
       <c r="C62" t="n">
-        <v>371.2</v>
+        <v>400.5</v>
       </c>
       <c r="D62" t="n">
         <v>14439.2</v>
@@ -5737,7 +5758,7 @@
         <v>33655.7</v>
       </c>
       <c r="R62" t="n">
-        <v>43708.5</v>
+        <v>43728</v>
       </c>
     </row>
     <row r="63">
@@ -5748,7 +5769,7 @@
         <v>6662.8</v>
       </c>
       <c r="C63" t="n">
-        <v>341.9</v>
+        <v>351.7</v>
       </c>
       <c r="D63" t="n">
         <v>15064.5</v>
@@ -5793,7 +5814,7 @@
         <v>19959</v>
       </c>
       <c r="R63" t="n">
-        <v>32649.5</v>
+        <v>32659.3</v>
       </c>
     </row>
     <row r="64">
@@ -5860,7 +5881,7 @@
         <v>6320.8</v>
       </c>
       <c r="C65" t="n">
-        <v>371.2</v>
+        <v>361.5</v>
       </c>
       <c r="D65" t="n">
         <v>24120.8</v>
@@ -5869,7 +5890,7 @@
         <v>5168</v>
       </c>
       <c r="F65" t="n">
-        <v>5089.9</v>
+        <v>5099.6</v>
       </c>
       <c r="G65" t="n">
         <v>9749.9</v>
@@ -5916,7 +5937,7 @@
         <v>6672.5</v>
       </c>
       <c r="C66" t="n">
-        <v>400.5</v>
+        <v>390.8</v>
       </c>
       <c r="D66" t="n">
         <v>23065.7</v>
@@ -5961,7 +5982,7 @@
         <v>-6662.8</v>
       </c>
       <c r="R66" t="n">
-        <v>19538.9</v>
+        <v>19529.1</v>
       </c>
     </row>
     <row r="67">
@@ -5972,7 +5993,7 @@
         <v>5715.1</v>
       </c>
       <c r="C67" t="n">
-        <v>390.8</v>
+        <v>381</v>
       </c>
       <c r="D67" t="n">
         <v>27305.6</v>
@@ -6017,7 +6038,7 @@
         <v>-16021.9</v>
       </c>
       <c r="R67" t="n">
-        <v>16109.8</v>
+        <v>16100</v>
       </c>
     </row>
     <row r="68">
@@ -6025,13 +6046,13 @@
         <v>46204</v>
       </c>
       <c r="B68" t="n">
-        <v>7151.2</v>
+        <v>7366.2</v>
       </c>
       <c r="C68" t="n">
-        <v>410.3</v>
+        <v>390.8</v>
       </c>
       <c r="D68" t="n">
-        <v>30119.2</v>
+        <v>29933.6</v>
       </c>
       <c r="E68" t="n">
         <v>15582.3</v>
@@ -6043,13 +6064,13 @@
         <v>4210.6</v>
       </c>
       <c r="H68" t="n">
-        <v>5822.6</v>
+        <v>5646.7</v>
       </c>
       <c r="I68" t="n">
         <v>595.9</v>
       </c>
       <c r="J68" t="n">
-        <v>14624.9</v>
+        <v>14634.6</v>
       </c>
       <c r="K68" t="n">
         <v>20261.8</v>
@@ -6073,7 +6094,7 @@
         <v>-14849.6</v>
       </c>
       <c r="R68" t="n">
-        <v>15142.6</v>
+        <v>15162.2</v>
       </c>
     </row>
     <row r="69">
@@ -6081,19 +6102,19 @@
         <v>46235</v>
       </c>
       <c r="B69" t="n">
-        <v>6486.9</v>
+        <v>7053.5</v>
       </c>
       <c r="C69" t="n">
-        <v>381</v>
+        <v>361.5</v>
       </c>
       <c r="D69" t="n">
-        <v>26006.3</v>
+        <v>25478.7</v>
       </c>
       <c r="E69" t="n">
         <v>19275.1</v>
       </c>
       <c r="F69" t="n">
-        <v>498.2</v>
+        <v>488.5</v>
       </c>
       <c r="G69" t="n">
         <v>762</v>
@@ -6102,16 +6123,16 @@
         <v>4259.5</v>
       </c>
       <c r="I69" t="n">
-        <v>1221.2</v>
+        <v>693.6</v>
       </c>
       <c r="J69" t="n">
-        <v>22587</v>
+        <v>22166.9</v>
       </c>
       <c r="K69" t="n">
-        <v>21864</v>
+        <v>21854.2</v>
       </c>
       <c r="L69" t="n">
-        <v>18298.2</v>
+        <v>18288.4</v>
       </c>
       <c r="M69" t="n">
         <v>3556.1</v>
@@ -6123,13 +6144,69 @@
         <v>1318.9</v>
       </c>
       <c r="P69" t="n">
-        <v>635</v>
+        <v>302.9</v>
       </c>
       <c r="Q69" t="n">
-        <v>-15338</v>
+        <v>-15279.4</v>
       </c>
       <c r="R69" t="n">
         <v>16305.2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>6223.1</v>
+      </c>
+      <c r="C70" t="n">
+        <v>312.6</v>
+      </c>
+      <c r="D70" t="n">
+        <v>23378.3</v>
+      </c>
+      <c r="E70" t="n">
+        <v>13901.9</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2041.8</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2628</v>
+      </c>
+      <c r="H70" t="n">
+        <v>3663.5</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1143</v>
+      </c>
+      <c r="J70" t="n">
+        <v>23055.9</v>
+      </c>
+      <c r="K70" t="n">
+        <v>17516.6</v>
+      </c>
+      <c r="L70" t="n">
+        <v>15758.1</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1758.5</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>703.4</v>
+      </c>
+      <c r="P70" t="n">
+        <v>752.2</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>-17731.5</v>
+      </c>
+      <c r="R70" t="n">
+        <v>16256.4</v>
       </c>
     </row>
   </sheetData>
